--- a/VibeProject1/Assets/Table/Trip/TripCityMap.xlsx
+++ b/VibeProject1/Assets/Table/Trip/TripCityMap.xlsx
@@ -14,8 +14,8 @@
   </x:bookViews>
   <x:sheets>
     <x:sheet name="TripCityStrings" sheetId="3" r:id="rId1"/>
-    <x:sheet name="TripCities" sheetId="8" r:id="rId7"/>
-    <x:sheet name="TripRoutes" sheetId="9" r:id="rId8"/>
+    <x:sheet name="TripCities" sheetId="10" r:id="rId7"/>
+    <x:sheet name="TripRoutes" sheetId="11" r:id="rId8"/>
   </x:sheets>
   <x:definedNames/>
   <x:calcPr calcId="0"/>
@@ -32,6 +32,9 @@
   </x:si>
   <x:si>
     <x:t>Description</x:t>
+  </x:si>
+  <x:si>
+    <x:t>디버그 도시 2</x:t>
   </x:si>
   <x:si>
     <x:r>
@@ -62,9 +65,6 @@
     <x:phoneticPr fontId="0" type="noConversion"/>
   </x:si>
   <x:si>
-    <x:t>디버그 도시 2</x:t>
-  </x:si>
-  <x:si>
     <x:t>설명2</x:t>
   </x:si>
   <x:si>
@@ -116,22 +116,22 @@
     <x:t>설명10</x:t>
   </x:si>
   <x:si>
+    <x:t>디버그 도시 11</x:t>
+  </x:si>
+  <x:si>
+    <x:t>값 없음</x:t>
+  </x:si>
+  <x:si>
+    <x:t>CityIdB</x:t>
+  </x:si>
+  <x:si>
+    <x:t>CityIdA</x:t>
+  </x:si>
+  <x:si>
     <x:t>Y</x:t>
   </x:si>
   <x:si>
     <x:t>X</x:t>
-  </x:si>
-  <x:si>
-    <x:t>값 없음</x:t>
-  </x:si>
-  <x:si>
-    <x:t>디버그 도시 11</x:t>
-  </x:si>
-  <x:si>
-    <x:t>CityIdA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>CityIdB</x:t>
   </x:si>
 </x:sst>
 </file>
@@ -491,7 +491,7 @@
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>
   <x:dimension ref="A1:C11"/>
-  <x:sheetFormatPr defaultColWidth="9.335625" defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
+  <x:sheetFormatPr defaultColWidth="9.460625" defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <x:cols>
     <x:col min="1" max="1" width="9.25" style="0" customWidth="1"/>
     <x:col min="2" max="2" width="16" style="0" customWidth="1"/>
@@ -514,10 +514,10 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="B2" s="0" t="s">
-        <x:v>3</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="C2" s="0" t="s">
-        <x:v>4</x:v>
+        <x:v>5</x:v>
       </x:c>
     </x:row>
     <x:row r="3" spans="1:3" x14ac:dyDescent="0.3">
@@ -525,7 +525,7 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="B3" s="0" t="s">
-        <x:v>5</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="C3" s="0" t="s">
         <x:v>6</x:v>
@@ -624,10 +624,10 @@
         <x:v>11</x:v>
       </x:c>
       <x:c r="B12" s="0" t="s">
-        <x:v>26</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="C12" s="0" t="s">
-        <x:v>25</x:v>
+        <x:v>24</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -645,7 +645,7 @@
   <x:sheetPr>
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>
-  <x:dimension ref="A1:C12"/>
+  <x:dimension ref="A1:C11"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:sheetData>
     <x:row r="1" spans="1:3">
@@ -653,10 +653,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="B1" s="0" t="s">
-        <x:v>24</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="C1" s="0" t="s">
-        <x:v>23</x:v>
+        <x:v>27</x:v>
       </x:c>
     </x:row>
     <x:row r="2" spans="1:3">
@@ -767,17 +767,6 @@
       </x:c>
       <x:c r="C11" s="0">
         <x:v>639.62548828125</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="12" spans="1:3">
-      <x:c r="A12" s="0">
-        <x:v>11</x:v>
-      </x:c>
-      <x:c r="B12" s="0">
-        <x:v>1127.53845214844</x:v>
-      </x:c>
-      <x:c r="C12" s="0">
-        <x:v>1997.24609375</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -799,10 +788,10 @@
   <x:sheetData>
     <x:row r="1" spans="1:2">
       <x:c r="A1" s="0" t="s">
-        <x:v>27</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="B1" s="0" t="s">
-        <x:v>28</x:v>
+        <x:v>25</x:v>
       </x:c>
     </x:row>
     <x:row r="2" spans="1:2">
